--- a/data-input/data-quality-definitions/grade_definitions.xlsx
+++ b/data-input/data-quality-definitions/grade_definitions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anavanderree/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anavanderree/Documents/GitHub/wid-world/data-input/data-quality-definitions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C44703-CF55-4749-B825-4C0DE36C6414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7F49CC-E886-6343-A0EE-F5CEC131FB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distributed variables (short de" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t>Wealth distribution is modeled using a hybrid of either income-capitalization techniques or wealth/estate tax tabulations and survey information, with rich list/national accounts adjustments.</t>
   </si>
   <si>
-    <t xml:space="preserve">No observation is classified with this score. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Surveys, but no tax data (for historical data: only tax data, no surveys). </t>
   </si>
   <si>
@@ -278,6 +275,9 @@
   </si>
   <si>
     <t>Values are directly observed from the UN World Population Prospects or from the most recent national accounts compiled under the latest SNA, representing the highest-quality data.</t>
+  </si>
+  <si>
+    <t>No observation is classified with this score. TEST</t>
   </si>
 </sst>
 </file>
@@ -781,10 +781,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>33</v>
@@ -795,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -827,13 +827,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -6933,7 +6933,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -6956,13 +6956,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="D7" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -13064,16 +13064,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -13096,16 +13096,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>65</v>
-      </c>
       <c r="D7" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -20119,7 +20119,7 @@
         <v>42</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -20142,16 +20142,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>60</v>
-      </c>
       <c r="D3" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="98">
@@ -20159,16 +20159,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="19" t="s">
         <v>71</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>72</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -20191,16 +20191,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="70">
@@ -20208,16 +20208,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -20240,16 +20240,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:20">

--- a/data-input/data-quality-definitions/grade_definitions.xlsx
+++ b/data-input/data-quality-definitions/grade_definitions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anavanderree/Documents/GitHub/wid-world/data-input/data-quality-definitions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7F49CC-E886-6343-A0EE-F5CEC131FB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9660FC02-E120-214C-A991-D492E0CDB506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,7 +277,7 @@
     <t>Values are directly observed from the UN World Population Prospects or from the most recent national accounts compiled under the latest SNA, representing the highest-quality data.</t>
   </si>
   <si>
-    <t>No observation is classified with this score. TEST</t>
+    <t>No observation is classified with this score.</t>
   </si>
 </sst>
 </file>

--- a/data-input/data-quality-definitions/grade_definitions.xlsx
+++ b/data-input/data-quality-definitions/grade_definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anavanderree/Documents/GitHub/wid-world/data-input/data-quality-definitions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9660FC02-E120-214C-A991-D492E0CDB506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91EB4D5-31F0-2943-A837-38212659ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distributed variables (short de" sheetId="1" r:id="rId1"/>
@@ -160,9 +160,6 @@
     <t>Wealth distribution is modeled using a hybrid of either income-capitalization techniques or wealth/estate tax tabulations and survey information, with rich list/national accounts adjustments.</t>
   </si>
   <si>
-    <t xml:space="preserve">Surveys, but no tax data (for historical data: only tax data, no surveys). </t>
-  </si>
-  <si>
     <t>Female and male wage and self-employment incomes are derived from a supplementary survey source. These observations are used to extend the time series beyond the years covered by the benchmark source, and are therefore of slightly lower priority but remain grounded in observed microdata.</t>
   </si>
   <si>
@@ -279,12 +276,15 @@
   <si>
     <t>No observation is classified with this score.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Only one type of source: survey data or tax data. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -336,6 +336,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -375,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -434,6 +441,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,15 +786,15 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="1:22" ht="42">
+    <row r="5" spans="1:22" ht="28">
       <c r="A5" s="9">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>45</v>
+      <c r="B5" s="21" t="s">
+        <v>84</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>33</v>
@@ -795,13 +805,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -827,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -6933,7 +6943,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -6956,13 +6966,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="D7" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -13064,16 +13074,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -13096,16 +13106,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>64</v>
-      </c>
       <c r="D7" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -20119,7 +20129,7 @@
         <v>42</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -20142,16 +20152,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>59</v>
-      </c>
       <c r="D3" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="98">
@@ -20159,16 +20169,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -20191,16 +20201,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="70">
@@ -20208,16 +20218,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -20240,16 +20250,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:20">
